--- a/docs/Vorschlag Arbeitsteilung - erweiterte Version.xlsx
+++ b/docs/Vorschlag Arbeitsteilung - erweiterte Version.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notebook\Documents\Studium\4. Semester\MAaS\Semesterprojekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notebook\Documents\Mobile-Applications-SS26\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592E0617-BFF8-461D-A391-BCCAD1FEA65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF34D87-F32E-460D-A1D7-7744ACF05835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{37DEA95C-12DA-4A15-A450-B2693DE4C3E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{37DEA95C-12DA-4A15-A450-B2693DE4C3E5}"/>
   </bookViews>
   <sheets>
-    <sheet name="ohne Erweiterung" sheetId="1" r:id="rId1"/>
-    <sheet name="mit Erweiterung" sheetId="2" r:id="rId2"/>
+    <sheet name="mit Erweiterung" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
   <si>
     <t>Requirement (original)</t>
   </si>
   <si>
-    <t>A/B</t>
-  </si>
-  <si>
     <t>Responsibility</t>
   </si>
   <si>
@@ -96,12 +92,6 @@
     <t>SQLite implementation</t>
   </si>
   <si>
-    <t>Synchronization of the local data with the data persisted on the server side: - if local todos exist, all remote todos are delete, and local todos are recreated remotely - if no local todos exist, all remote todos are replicated to the local database</t>
-  </si>
-  <si>
-    <t>Synchronization logic</t>
-  </si>
-  <si>
     <t>If the web application is not available when starting the mobile app, a suitable notification should be displayed. In this case, only the local database is used for the entire usage time of the application</t>
   </si>
   <si>
@@ -120,9 +110,6 @@
     <t>Only email addresses should be entered in the input field for email</t>
   </si>
   <si>
-    <t>Validation</t>
-  </si>
-  <si>
     <t>If no email address is entered, an error message will be displayed.</t>
   </si>
   <si>
@@ -147,9 +134,6 @@
     <t>The check is supposed to be asynchronous.</t>
   </si>
   <si>
-    <t>Async request</t>
-  </si>
-  <si>
     <t>a suitable progress indication should be given while the remote asynchronous check is in progress.</t>
   </si>
   <si>
@@ -168,21 +152,9 @@
     <t>If the entered values are successfully checked, the todos should be displayed.</t>
   </si>
   <si>
-    <t>A + B</t>
-  </si>
-  <si>
-    <t>Login → TodoList</t>
-  </si>
-  <si>
     <t>if the web application is not reachable when starting the mobile application, the todo list should be displayed directly. Local login is not necessary.</t>
   </si>
   <si>
-    <t>Offline start</t>
-  </si>
-  <si>
-    <t>Todo list</t>
-  </si>
-  <si>
     <t>The display of the todo list should provide an overview of all todos and allow for the creation of new todos.</t>
   </si>
   <si>
@@ -192,9 +164,6 @@
     <t>the name</t>
   </si>
   <si>
-    <t>RecyclerView item</t>
-  </si>
-  <si>
     <t>the due date</t>
   </si>
   <si>
@@ -213,15 +182,9 @@
     <t>Changes to the todo list that can be made in the detail view of a todo should be displayed in the overview when you return.</t>
   </si>
   <si>
-    <t>Refresh/update</t>
-  </si>
-  <si>
     <t>It should be possible to modify the information on the done/not done or the importance without requesting the detailed display.</t>
   </si>
   <si>
-    <t>Direct actions in list</t>
-  </si>
-  <si>
     <t>Todos should always be sorted by done/not done and then either by importance+date or by date+importance.</t>
   </si>
   <si>
@@ -240,9 +203,6 @@
     <t>Visual highlighting</t>
   </si>
   <si>
-    <t>Details view</t>
-  </si>
-  <si>
     <t>The detail view is intended to display all data represented by a todo.</t>
   </si>
   <si>
@@ -252,9 +212,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Edit field</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -267,9 +224,6 @@
     <t>Finished state</t>
   </si>
   <si>
-    <t>Checkbox/Switch</t>
-  </si>
-  <si>
     <t>For setting date and time, suitable UI controls should be used.</t>
   </si>
   <si>
@@ -285,91 +239,25 @@
     <t>Documentation of your application using a UML class diagramm</t>
   </si>
   <si>
-    <t>UML</t>
-  </si>
-  <si>
     <t>Focus on architecturally relevant classes, attributes, methods, and relations. Do not auto-reverse-engineer your code.</t>
   </si>
   <si>
-    <t>Task</t>
-  </si>
-  <si>
     <t>Todo class definition</t>
   </si>
   <si>
-    <t>Common data model</t>
-  </si>
-  <si>
     <t>Repository interface definition</t>
   </si>
   <si>
-    <t>Common contract</t>
-  </si>
-  <si>
     <t>Repository implementation</t>
   </si>
   <si>
-    <t>SQLite + Server</t>
-  </si>
-  <si>
     <t>UI implementation against repository</t>
   </si>
   <si>
-    <t>Activities and views</t>
-  </si>
-  <si>
     <t>Integration</t>
   </si>
   <si>
-    <t>Merge components</t>
-  </si>
-  <si>
     <t>Testing</t>
-  </si>
-  <si>
-    <t>Verification and bug fixing</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">So habt ihr die Anforderungen tatsächlich </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1:1 aus der PDF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, ergänzt um die Zuordnung, wer welchen Punkt umsetzt.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Additional project work </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(steht nicht mehr in Schafföners Liste, aber laut KI notwendig)</t>
-    </r>
   </si>
   <si>
     <t>Data Model</t>
@@ -565,7 +453,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,23 +471,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13.5"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -647,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,21 +527,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1005,685 +871,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E04F69-F5C7-46F5-87AB-FA38C8C56277}">
-  <dimension ref="A2:C78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="55.77734375" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>97</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B7EC9-B91C-41BE-B2E7-6403BA2128DE}">
   <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1695,8 +882,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>99</v>
+      <c r="A1" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1704,90 +891,90 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,81 +982,81 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>23</v>
+      <c r="A23" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1877,169 +1064,169 @@
         <v>0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>112</v>
+      <c r="A42" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2047,136 +1234,136 @@
         <v>0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>116</v>
+      <c r="A58" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -2184,92 +1371,92 @@
         <v>0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>80</v>
+      <c r="A70" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2277,43 +1464,43 @@
         <v>0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>119</v>
+      <c r="A77" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2321,253 +1508,253 @@
         <v>0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
+      <c r="A92" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D102" s="9" t="s">
-        <v>152</v>
+      <c r="D102" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Vorschlag Arbeitsteilung - erweiterte Version.xlsx
+++ b/docs/Vorschlag Arbeitsteilung - erweiterte Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Notebook\Documents\Mobile-Applications-SS26\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF34D87-F32E-460D-A1D7-7744ACF05835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C68240-9737-4388-8AEF-B3085B965BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{37DEA95C-12DA-4A15-A450-B2693DE4C3E5}"/>
   </bookViews>
@@ -437,9 +437,6 @@
     <t>keine externen libraries mit downloads</t>
   </si>
   <si>
-    <t>camelCase</t>
-  </si>
-  <si>
     <t>Klassennamen mit Anfangsbuchstaben gemäß Fkt. (zb I bei Interface)</t>
   </si>
   <si>
@@ -447,6 +444,9 @@
   </si>
   <si>
     <t>Package-Struktur gemäß Intellij</t>
+  </si>
+  <si>
+    <t>CamelCase</t>
   </si>
 </sst>
 </file>
@@ -1739,22 +1739,22 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
